--- a/examples/demos/03_fit_copula_and_wire.xlsx
+++ b/examples/demos/03_fit_copula_and_wire.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B11BF2E-0138-4F44-8C3B-A9F853ED7261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A93D14-962A-49BB-885A-690A0C87761E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="66">
   <si>
     <t>Demo 03 — Fit dependence from data and wire a correlated model</t>
   </si>
@@ -55,16 +55,31 @@
     <t>Tools demonstrated: fit_copula_to_data, fit_all_data_and_wire, run_simulation, get_simulation_results</t>
   </si>
   <si>
-    <t>PREREQUISITES</t>
-  </si>
-  <si>
-    <t>Windows Excel with the ModelRisk add-in installed and licensed.</t>
-  </si>
-  <si>
-    <t>modelrisk-mcp connected to Claude (Claude Desktop / Claude Code).</t>
-  </si>
-  <si>
-    <t>PROMPT →  Open C:/Users/timou/source/repos/modelrisk-mcp/examples/demos/03_fit_copula_and_wire.xlsx in Excel</t>
+    <t>GETTING STARTED</t>
+  </si>
+  <si>
+    <t>You need: Windows Excel with the ModelRisk add-in installed and licensed, and modelrisk-mcp connected to Claude (Claude Desktop or Claude Code).</t>
+  </si>
+  <si>
+    <t>Save the demo gallery folder anywhere on your PC. Once per session, tell Claude where it is and which demo to open:</t>
+  </si>
+  <si>
+    <t>PROMPT →  My ModelRisk demo gallery is in &lt;your folder, e.g. Documents\modelrisk-demos&gt;. Open 03_fit_copula_and_wire.xlsx from there.</t>
+  </si>
+  <si>
+    <t>Claude remembers the folder for the rest of the session — later demos just need "Open &lt;file&gt; from the demo folder".</t>
+  </si>
+  <si>
+    <t>FAST TRACK — ONE PROMPT DOES IT ALL</t>
+  </si>
+  <si>
+    <t>In a hurry? This single prompt runs the whole demo end-to-end. Prefer to learn how it works? Skip to the numbered steps below — same result, one capability at a time.</t>
+  </si>
+  <si>
+    <t>PROMPT →  Fit copulas to 'Data'!A5:C244 of this workbook and tell me the best family and its tail dependence. Then fit the marginals and the copula and wire them into Model!B10, B11 and B12 with input names Steel, Diesel and Labour and the copula block at H6 — for real — and run 5,000 iterations. Give me the P80 total cost and one sentence on why the correlation matters here.</t>
+  </si>
+  <si>
+    <t>Expected: a correlated, simulation-validated cost model wired from raw data, plus the P80.</t>
   </si>
   <si>
     <t>STEP-BY-STEP</t>
@@ -74,6 +89,9 @@
   </si>
   <si>
     <t>Open the workbook in Excel.</t>
+  </si>
+  <si>
+    <t>PROMPT →  Open 03_fit_copula_and_wire.xlsx from the demo folder.</t>
   </si>
   <si>
     <t>Expected: the workbook opens with README, Data and Model sheets.</t>
@@ -224,13 +242,53 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -279,12 +337,42 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E4F92"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECF4FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -329,38 +417,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -669,7 +763,7 @@
   <sheetPr>
     <tabColor rgb="FF0E4F92"/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -677,215 +771,242 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
+      <c r="B1" s="21"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
+      <c r="B2" s="19"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16"/>
+      <c r="B4" s="17"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="9" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="16"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
+      <c r="B9" s="17"/>
+    </row>
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="15" t="s">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="16"/>
-    </row>
-    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="15" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="17"/>
+    </row>
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="4" t="s">
+    <row r="17" spans="1:2" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="3" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="B18" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="17"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A21" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="3" t="s">
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="11" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="2" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="3" t="s">
+    <row r="26" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="1" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B28" s="2" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A29" s="12" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="3" t="s">
+    <row r="30" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="1" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="2" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A33" s="12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="15" t="s">
+    <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="16"/>
-    </row>
-    <row r="36" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="4" t="s">
+    </row>
+    <row r="35" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="4" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A37" s="12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B38" s="4" t="s">
+      <c r="B37" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="15" t="s">
+    <row r="38" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B40" s="16"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A41" s="5"/>
-      <c r="B41" s="1" t="s">
+    </row>
+    <row r="39" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="11" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A42" s="6"/>
-      <c r="B42" s="1" t="s">
+    <row r="41" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A43" s="7"/>
-      <c r="B43" s="1" t="s">
+      <c r="B41" s="17"/>
+    </row>
+    <row r="42" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A44" s="2"/>
-      <c r="B44" s="1" t="s">
+    <row r="43" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="9" t="s">
         <v>38</v>
       </c>
     </row>
+    <row r="44" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B44" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="17"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A47" s="13"/>
+      <c r="B47" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A48" s="14"/>
+      <c r="B48" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.5">
+      <c r="A49" s="15"/>
+      <c r="B49" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A50" s="10"/>
+      <c r="B50" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A9:B9"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A41:B41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -905,2674 +1026,2674 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
+      <c r="A1" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
+      <c r="A2" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>43</v>
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="9">
+      <c r="A5" s="3">
         <v>629.99</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="4">
         <v>0.94</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="4">
         <v>95.28</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>44</v>
+      <c r="E5" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A6" s="9">
+      <c r="A6" s="3">
         <v>634.96</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="4">
         <v>0.95</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="4">
         <v>98.13</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A7" s="9">
+      <c r="A7" s="3">
         <v>615.55999999999995</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="4">
         <v>0.88</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="4">
         <v>92.79</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A8" s="9">
+      <c r="A8" s="3">
         <v>766.37</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="4">
         <v>1.25</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="4">
         <v>107.15</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A9" s="9">
+      <c r="A9" s="3">
         <v>740.94</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="4">
         <v>0.96</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="4">
         <v>107.86</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A10" s="9">
+      <c r="A10" s="3">
         <v>704.53</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="4">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="4">
         <v>99.96</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A11" s="9">
+      <c r="A11" s="3">
         <v>612.22</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="4">
         <v>0.93</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="4">
         <v>92.29</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A12" s="9">
+      <c r="A12" s="3">
         <v>711.34</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="4">
         <v>1.05</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="4">
         <v>109.15</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A13" s="9">
+      <c r="A13" s="3">
         <v>842.07</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="4">
         <v>102.94</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="9">
+      <c r="A14" s="3">
         <v>678.22</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="4">
         <v>98.59</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="9">
+      <c r="A15" s="3">
         <v>663.12</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="4">
         <v>0.97</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="4">
         <v>98.03</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="9">
+      <c r="A16" s="3">
         <v>726.43</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="4">
         <v>0.95</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="4">
         <v>95.97</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17" s="9">
+      <c r="A17" s="3">
         <v>747.94</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="4">
         <v>1.07</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17" s="4">
         <v>104.68</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" s="9">
+      <c r="A18" s="3">
         <v>747.81</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="4">
         <v>1.07</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C18" s="4">
         <v>104.8</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A19" s="9">
+      <c r="A19" s="3">
         <v>591.55999999999995</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="4">
         <v>0.87</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="4">
         <v>92.15</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A20" s="9">
+      <c r="A20" s="3">
         <v>755.62</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="4">
         <v>1</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="4">
         <v>97.19</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A21" s="9">
+      <c r="A21" s="3">
         <v>701.16</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="4">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="4">
         <v>100.47</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A22" s="9">
+      <c r="A22" s="3">
         <v>738.62</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="4">
         <v>1.18</v>
       </c>
-      <c r="C22" s="10">
+      <c r="C22" s="4">
         <v>114.52</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A23" s="9">
+      <c r="A23" s="3">
         <v>598.79</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="4">
         <v>0.82</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="4">
         <v>90.2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A24" s="9">
+      <c r="A24" s="3">
         <v>831.54</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="4">
         <v>1.18</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="4">
         <v>97.77</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A25" s="9">
+      <c r="A25" s="3">
         <v>877.91</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="4">
         <v>110.1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A26" s="9">
+      <c r="A26" s="3">
         <v>661.02</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="4">
         <v>0.96</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="4">
         <v>100.89</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A27" s="9">
+      <c r="A27" s="3">
         <v>637.99</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="4">
         <v>0.86</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="4">
         <v>91.82</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A28" s="9">
+      <c r="A28" s="3">
         <v>901.97</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="4">
         <v>1.18</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="4">
         <v>109.47</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A29" s="9">
+      <c r="A29" s="3">
         <v>676.81</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="4">
         <v>0.98</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="4">
         <v>96.65</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A30" s="9">
+      <c r="A30" s="3">
         <v>600.54</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="4">
         <v>0.89</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="4">
         <v>92.61</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A31" s="9">
+      <c r="A31" s="3">
         <v>598.92999999999995</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="4">
         <v>0.84</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="4">
         <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A32" s="9">
+      <c r="A32" s="3">
         <v>688.06</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="4">
         <v>1.06</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="4">
         <v>98.38</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A33" s="9">
+      <c r="A33" s="3">
         <v>718.66</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="4">
         <v>101.83</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A34" s="9">
+      <c r="A34" s="3">
         <v>605.17999999999995</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="4">
         <v>0.9</v>
       </c>
-      <c r="C34" s="10">
+      <c r="C34" s="4">
         <v>90.92</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A35" s="9">
+      <c r="A35" s="3">
         <v>712.4</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C35" s="10">
+      <c r="C35" s="4">
         <v>104.5</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A36" s="9">
+      <c r="A36" s="3">
         <v>688.37</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="4">
         <v>1.06</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C36" s="4">
         <v>109.25</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A37" s="9">
+      <c r="A37" s="3">
         <v>607.70000000000005</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="4">
         <v>0.89</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="4">
         <v>95.33</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A38" s="9">
+      <c r="A38" s="3">
         <v>677.69</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="4">
         <v>0.98</v>
       </c>
-      <c r="C38" s="10">
+      <c r="C38" s="4">
         <v>95.43</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A39" s="9">
+      <c r="A39" s="3">
         <v>731.98</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="4">
         <v>1.07</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C39" s="4">
         <v>99.47</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A40" s="9">
+      <c r="A40" s="3">
         <v>741.28</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="4">
         <v>0.96</v>
       </c>
-      <c r="C40" s="10">
+      <c r="C40" s="4">
         <v>98.28</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A41" s="9">
+      <c r="A41" s="3">
         <v>699.11</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="4">
         <v>0.96</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="4">
         <v>101.29</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A42" s="9">
+      <c r="A42" s="3">
         <v>832.6</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="4">
         <v>1.05</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="4">
         <v>104.46</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A43" s="9">
+      <c r="A43" s="3">
         <v>615.07000000000005</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="4">
         <v>0.9</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="4">
         <v>93.6</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A44" s="9">
+      <c r="A44" s="3">
         <v>682.32</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="4">
         <v>0.93</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="4">
         <v>95.54</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A45" s="9">
+      <c r="A45" s="3">
         <v>748.34</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="4">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="4">
         <v>107.17</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A46" s="9">
+      <c r="A46" s="3">
         <v>682.08</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C46" s="10">
+      <c r="C46" s="4">
         <v>106.73</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A47" s="9">
+      <c r="A47" s="3">
         <v>695.76</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C47" s="10">
+      <c r="C47" s="4">
         <v>103.58</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A48" s="9">
+      <c r="A48" s="3">
         <v>658.65</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="4">
         <v>0.91</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="4">
         <v>93.74</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A49" s="9">
+      <c r="A49" s="3">
         <v>619.48</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="4">
         <v>0.92</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="4">
         <v>92.27</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A50" s="9">
+      <c r="A50" s="3">
         <v>788.56</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="4">
         <v>1.31</v>
       </c>
-      <c r="C50" s="10">
+      <c r="C50" s="4">
         <v>105.82</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A51" s="9">
+      <c r="A51" s="3">
         <v>737.46</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="4">
         <v>1.05</v>
       </c>
-      <c r="C51" s="10">
+      <c r="C51" s="4">
         <v>105.42</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A52" s="9">
+      <c r="A52" s="3">
         <v>632.84</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="4">
         <v>1.05</v>
       </c>
-      <c r="C52" s="10">
+      <c r="C52" s="4">
         <v>94.11</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A53" s="9">
+      <c r="A53" s="3">
         <v>664.69</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="4">
         <v>0.97</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C53" s="4">
         <v>97.19</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A54" s="9">
+      <c r="A54" s="3">
         <v>602.09</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="4">
         <v>0.89</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="4">
         <v>96.22</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A55" s="9">
+      <c r="A55" s="3">
         <v>677.87</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="4">
         <v>1.07</v>
       </c>
-      <c r="C55" s="10">
+      <c r="C55" s="4">
         <v>97.87</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A56" s="9">
+      <c r="A56" s="3">
         <v>680.87</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="4">
         <v>1</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C56" s="4">
         <v>97.92</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A57" s="9">
+      <c r="A57" s="3">
         <v>699.01</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C57" s="10">
+      <c r="C57" s="4">
         <v>98.15</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A58" s="9">
+      <c r="A58" s="3">
         <v>585.16999999999996</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="4">
         <v>0.82</v>
       </c>
-      <c r="C58" s="10">
+      <c r="C58" s="4">
         <v>90.61</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A59" s="9">
+      <c r="A59" s="3">
         <v>734.39</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="4">
         <v>1.18</v>
       </c>
-      <c r="C59" s="10">
+      <c r="C59" s="4">
         <v>100.43</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A60" s="9">
+      <c r="A60" s="3">
         <v>650.73</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="4">
         <v>1.07</v>
       </c>
-      <c r="C60" s="10">
+      <c r="C60" s="4">
         <v>102.95</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A61" s="9">
+      <c r="A61" s="3">
         <v>675.27</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="4">
         <v>1</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="4">
         <v>95.72</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A62" s="9">
+      <c r="A62" s="3">
         <v>683.04</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="4">
         <v>1.01</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C62" s="4">
         <v>96.34</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A63" s="9">
+      <c r="A63" s="3">
         <v>671.8</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="4">
         <v>0.91</v>
       </c>
-      <c r="C63" s="10">
+      <c r="C63" s="4">
         <v>97.74</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A64" s="9">
+      <c r="A64" s="3">
         <v>754.27</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="4">
         <v>1.46</v>
       </c>
-      <c r="C64" s="10">
+      <c r="C64" s="4">
         <v>103.21</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A65" s="9">
+      <c r="A65" s="3">
         <v>686.83</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="4">
         <v>1.02</v>
       </c>
-      <c r="C65" s="10">
+      <c r="C65" s="4">
         <v>101.17</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A66" s="9">
+      <c r="A66" s="3">
         <v>717.96</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="4">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C66" s="10">
+      <c r="C66" s="4">
         <v>103.89</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A67" s="9">
+      <c r="A67" s="3">
         <v>620.55999999999995</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="4">
         <v>0.93</v>
       </c>
-      <c r="C67" s="10">
+      <c r="C67" s="4">
         <v>91.18</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A68" s="9">
+      <c r="A68" s="3">
         <v>584.54</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="4">
         <v>0.9</v>
       </c>
-      <c r="C68" s="10">
+      <c r="C68" s="4">
         <v>90.71</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A69" s="9">
+      <c r="A69" s="3">
         <v>688.84</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="4">
         <v>1.17</v>
       </c>
-      <c r="C69" s="10">
+      <c r="C69" s="4">
         <v>104.48</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A70" s="9">
+      <c r="A70" s="3">
         <v>711.73</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="4">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C70" s="10">
+      <c r="C70" s="4">
         <v>105.24</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A71" s="9">
+      <c r="A71" s="3">
         <v>718.34</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="4">
         <v>1.02</v>
       </c>
-      <c r="C71" s="10">
+      <c r="C71" s="4">
         <v>105.65</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A72" s="9">
+      <c r="A72" s="3">
         <v>632.74</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="4">
         <v>0.95</v>
       </c>
-      <c r="C72" s="10">
+      <c r="C72" s="4">
         <v>95.66</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A73" s="9">
+      <c r="A73" s="3">
         <v>717.7</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="4">
         <v>1.04</v>
       </c>
-      <c r="C73" s="10">
+      <c r="C73" s="4">
         <v>101.72</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A74" s="9">
+      <c r="A74" s="3">
         <v>703.49</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="4">
         <v>1.02</v>
       </c>
-      <c r="C74" s="10">
+      <c r="C74" s="4">
         <v>97.7</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A75" s="9">
+      <c r="A75" s="3">
         <v>637.29</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="4">
         <v>1</v>
       </c>
-      <c r="C75" s="10">
+      <c r="C75" s="4">
         <v>98.12</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A76" s="9">
+      <c r="A76" s="3">
         <v>648.72</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="4">
         <v>1.01</v>
       </c>
-      <c r="C76" s="10">
+      <c r="C76" s="4">
         <v>99.55</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A77" s="9">
+      <c r="A77" s="3">
         <v>652.34</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="4">
         <v>0.97</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C77" s="4">
         <v>96.11</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A78" s="9">
+      <c r="A78" s="3">
         <v>663.15</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="4">
         <v>1</v>
       </c>
-      <c r="C78" s="10">
+      <c r="C78" s="4">
         <v>99.07</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A79" s="9">
+      <c r="A79" s="3">
         <v>724.8</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="4">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C79" s="10">
+      <c r="C79" s="4">
         <v>100.65</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A80" s="9">
+      <c r="A80" s="3">
         <v>711.66</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="4">
         <v>0.96</v>
       </c>
-      <c r="C80" s="10">
+      <c r="C80" s="4">
         <v>101.48</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A81" s="9">
+      <c r="A81" s="3">
         <v>634.11</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="4">
         <v>0.9</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C81" s="4">
         <v>92.53</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A82" s="9">
+      <c r="A82" s="3">
         <v>622.29</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="4">
         <v>1.06</v>
       </c>
-      <c r="C82" s="10">
+      <c r="C82" s="4">
         <v>93.48</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A83" s="9">
+      <c r="A83" s="3">
         <v>690.5</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="4">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C83" s="10">
+      <c r="C83" s="4">
         <v>108.08</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A84" s="9">
+      <c r="A84" s="3">
         <v>721.87</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C84" s="10">
+      <c r="C84" s="4">
         <v>109.75</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A85" s="9">
+      <c r="A85" s="3">
         <v>665.71</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="4">
         <v>1</v>
       </c>
-      <c r="C85" s="10">
+      <c r="C85" s="4">
         <v>102</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A86" s="9">
+      <c r="A86" s="3">
         <v>667.35</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C86" s="4">
         <v>100.16</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A87" s="9">
+      <c r="A87" s="3">
         <v>790</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="4">
         <v>1.29</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C87" s="4">
         <v>105.43</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A88" s="9">
+      <c r="A88" s="3">
         <v>693.83</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C88" s="10">
+      <c r="C88" s="4">
         <v>103.63</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A89" s="9">
+      <c r="A89" s="3">
         <v>720.38</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="4">
         <v>1.27</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C89" s="4">
         <v>104.98</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A90" s="9">
+      <c r="A90" s="3">
         <v>731.23</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="4">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C90" s="10">
+      <c r="C90" s="4">
         <v>102.23</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A91" s="9">
+      <c r="A91" s="3">
         <v>739.68</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="4">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C91" s="10">
+      <c r="C91" s="4">
         <v>111.25</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A92" s="9">
+      <c r="A92" s="3">
         <v>702.95</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="4">
         <v>1.04</v>
       </c>
-      <c r="C92" s="10">
+      <c r="C92" s="4">
         <v>98.9</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A93" s="9">
+      <c r="A93" s="3">
         <v>667.11</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="4">
         <v>0.89</v>
       </c>
-      <c r="C93" s="10">
+      <c r="C93" s="4">
         <v>95.67</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A94" s="9">
+      <c r="A94" s="3">
         <v>681.04</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C94" s="10">
+      <c r="C94" s="4">
         <v>97.38</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A95" s="9">
+      <c r="A95" s="3">
         <v>666.9</v>
       </c>
-      <c r="B95" s="10">
+      <c r="B95" s="4">
         <v>1.06</v>
       </c>
-      <c r="C95" s="10">
+      <c r="C95" s="4">
         <v>97.63</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A96" s="9">
+      <c r="A96" s="3">
         <v>637.97</v>
       </c>
-      <c r="B96" s="10">
+      <c r="B96" s="4">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C96" s="10">
+      <c r="C96" s="4">
         <v>100.47</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A97" s="9">
+      <c r="A97" s="3">
         <v>695.83</v>
       </c>
-      <c r="B97" s="10">
+      <c r="B97" s="4">
         <v>1.01</v>
       </c>
-      <c r="C97" s="10">
+      <c r="C97" s="4">
         <v>97.9</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A98" s="9">
+      <c r="A98" s="3">
         <v>836.82</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="4">
         <v>1.17</v>
       </c>
-      <c r="C98" s="10">
+      <c r="C98" s="4">
         <v>100.94</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A99" s="9">
+      <c r="A99" s="3">
         <v>747.99</v>
       </c>
-      <c r="B99" s="10">
+      <c r="B99" s="4">
         <v>0.92</v>
       </c>
-      <c r="C99" s="10">
+      <c r="C99" s="4">
         <v>100.51</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A100" s="9">
+      <c r="A100" s="3">
         <v>612.33000000000004</v>
       </c>
-      <c r="B100" s="10">
+      <c r="B100" s="4">
         <v>0.98</v>
       </c>
-      <c r="C100" s="10">
+      <c r="C100" s="4">
         <v>93.15</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A101" s="9">
+      <c r="A101" s="3">
         <v>647.91999999999996</v>
       </c>
-      <c r="B101" s="10">
+      <c r="B101" s="4">
         <v>1.21</v>
       </c>
-      <c r="C101" s="10">
+      <c r="C101" s="4">
         <v>94.19</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A102" s="9">
+      <c r="A102" s="3">
         <v>668.5</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B102" s="4">
         <v>0.91</v>
       </c>
-      <c r="C102" s="10">
+      <c r="C102" s="4">
         <v>97.85</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A103" s="9">
+      <c r="A103" s="3">
         <v>637.34</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="4">
         <v>0.96</v>
       </c>
-      <c r="C103" s="10">
+      <c r="C103" s="4">
         <v>107.37</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A104" s="9">
+      <c r="A104" s="3">
         <v>754.73</v>
       </c>
-      <c r="B104" s="10">
+      <c r="B104" s="4">
         <v>1.52</v>
       </c>
-      <c r="C104" s="10">
+      <c r="C104" s="4">
         <v>111.86</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A105" s="9">
+      <c r="A105" s="3">
         <v>672.65</v>
       </c>
-      <c r="B105" s="10">
+      <c r="B105" s="4">
         <v>1.24</v>
       </c>
-      <c r="C105" s="10">
+      <c r="C105" s="4">
         <v>97.31</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A106" s="9">
+      <c r="A106" s="3">
         <v>631.80999999999995</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="4">
         <v>0.97</v>
       </c>
-      <c r="C106" s="10">
+      <c r="C106" s="4">
         <v>93.44</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A107" s="9">
+      <c r="A107" s="3">
         <v>586.41999999999996</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="4">
         <v>0.85</v>
       </c>
-      <c r="C107" s="10">
+      <c r="C107" s="4">
         <v>90.93</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A108" s="9">
+      <c r="A108" s="3">
         <v>636.54</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="4">
         <v>0.94</v>
       </c>
-      <c r="C108" s="10">
+      <c r="C108" s="4">
         <v>96.82</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A109" s="9">
+      <c r="A109" s="3">
         <v>619.33000000000004</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="4">
         <v>0.85</v>
       </c>
-      <c r="C109" s="10">
+      <c r="C109" s="4">
         <v>92.59</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A110" s="9">
+      <c r="A110" s="3">
         <v>794.97</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="4">
         <v>1.35</v>
       </c>
-      <c r="C110" s="10">
+      <c r="C110" s="4">
         <v>110.4</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A111" s="9">
+      <c r="A111" s="3">
         <v>710.72</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="4">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C111" s="10">
+      <c r="C111" s="4">
         <v>96.54</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A112" s="9">
+      <c r="A112" s="3">
         <v>760.08</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="4">
         <v>1.19</v>
       </c>
-      <c r="C112" s="10">
+      <c r="C112" s="4">
         <v>103.25</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A113" s="9">
+      <c r="A113" s="3">
         <v>730.26</v>
       </c>
-      <c r="B113" s="10">
+      <c r="B113" s="4">
         <v>1.19</v>
       </c>
-      <c r="C113" s="10">
+      <c r="C113" s="4">
         <v>102.34</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A114" s="9">
+      <c r="A114" s="3">
         <v>620.39</v>
       </c>
-      <c r="B114" s="10">
+      <c r="B114" s="4">
         <v>1.03</v>
       </c>
-      <c r="C114" s="10">
+      <c r="C114" s="4">
         <v>96.37</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A115" s="9">
+      <c r="A115" s="3">
         <v>621.87</v>
       </c>
-      <c r="B115" s="10">
+      <c r="B115" s="4">
         <v>0.89</v>
       </c>
-      <c r="C115" s="10">
+      <c r="C115" s="4">
         <v>94.82</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A116" s="9">
+      <c r="A116" s="3">
         <v>804.64</v>
       </c>
-      <c r="B116" s="10">
+      <c r="B116" s="4">
         <v>1.26</v>
       </c>
-      <c r="C116" s="10">
+      <c r="C116" s="4">
         <v>104.53</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A117" s="9">
+      <c r="A117" s="3">
         <v>730.16</v>
       </c>
-      <c r="B117" s="10">
+      <c r="B117" s="4">
         <v>1.01</v>
       </c>
-      <c r="C117" s="10">
+      <c r="C117" s="4">
         <v>101.34</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A118" s="9">
+      <c r="A118" s="3">
         <v>860.16</v>
       </c>
-      <c r="B118" s="10">
+      <c r="B118" s="4">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C118" s="10">
+      <c r="C118" s="4">
         <v>113.15</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A119" s="9">
+      <c r="A119" s="3">
         <v>775.47</v>
       </c>
-      <c r="B119" s="10">
+      <c r="B119" s="4">
         <v>1.1299999999999999</v>
       </c>
-      <c r="C119" s="10">
+      <c r="C119" s="4">
         <v>113.99</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A120" s="9">
+      <c r="A120" s="3">
         <v>752.23</v>
       </c>
-      <c r="B120" s="10">
+      <c r="B120" s="4">
         <v>1.04</v>
       </c>
-      <c r="C120" s="10">
+      <c r="C120" s="4">
         <v>99.55</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A121" s="9">
+      <c r="A121" s="3">
         <v>623.67999999999995</v>
       </c>
-      <c r="B121" s="10">
+      <c r="B121" s="4">
         <v>0.96</v>
       </c>
-      <c r="C121" s="10">
+      <c r="C121" s="4">
         <v>97.38</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A122" s="9">
+      <c r="A122" s="3">
         <v>738.57</v>
       </c>
-      <c r="B122" s="10">
+      <c r="B122" s="4">
         <v>1.01</v>
       </c>
-      <c r="C122" s="10">
+      <c r="C122" s="4">
         <v>106.77</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A123" s="9">
+      <c r="A123" s="3">
         <v>689.95</v>
       </c>
-      <c r="B123" s="10">
+      <c r="B123" s="4">
         <v>1.1200000000000001</v>
       </c>
-      <c r="C123" s="10">
+      <c r="C123" s="4">
         <v>109.4</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A124" s="9">
+      <c r="A124" s="3">
         <v>698.67</v>
       </c>
-      <c r="B124" s="10">
+      <c r="B124" s="4">
         <v>0.99</v>
       </c>
-      <c r="C124" s="10">
+      <c r="C124" s="4">
         <v>99.48</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A125" s="9">
+      <c r="A125" s="3">
         <v>791.1</v>
       </c>
-      <c r="B125" s="10">
+      <c r="B125" s="4">
         <v>1.27</v>
       </c>
-      <c r="C125" s="10">
+      <c r="C125" s="4">
         <v>104.61</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A126" s="9">
+      <c r="A126" s="3">
         <v>664.86</v>
       </c>
-      <c r="B126" s="10">
+      <c r="B126" s="4">
         <v>0.96</v>
       </c>
-      <c r="C126" s="10">
+      <c r="C126" s="4">
         <v>98.32</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A127" s="9">
+      <c r="A127" s="3">
         <v>700.6</v>
       </c>
-      <c r="B127" s="10">
+      <c r="B127" s="4">
         <v>1.03</v>
       </c>
-      <c r="C127" s="10">
+      <c r="C127" s="4">
         <v>100.76</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A128" s="9">
+      <c r="A128" s="3">
         <v>709.29</v>
       </c>
-      <c r="B128" s="10">
+      <c r="B128" s="4">
         <v>0.99</v>
       </c>
-      <c r="C128" s="10">
+      <c r="C128" s="4">
         <v>98.59</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A129" s="9">
+      <c r="A129" s="3">
         <v>702.56</v>
       </c>
-      <c r="B129" s="10">
+      <c r="B129" s="4">
         <v>1.08</v>
       </c>
-      <c r="C129" s="10">
+      <c r="C129" s="4">
         <v>104.48</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A130" s="9">
+      <c r="A130" s="3">
         <v>766.81</v>
       </c>
-      <c r="B130" s="10">
+      <c r="B130" s="4">
         <v>1.28</v>
       </c>
-      <c r="C130" s="10">
+      <c r="C130" s="4">
         <v>108.59</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A131" s="9">
+      <c r="A131" s="3">
         <v>706.98</v>
       </c>
-      <c r="B131" s="10">
+      <c r="B131" s="4">
         <v>1.21</v>
       </c>
-      <c r="C131" s="10">
+      <c r="C131" s="4">
         <v>106.64</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A132" s="9">
+      <c r="A132" s="3">
         <v>685.72</v>
       </c>
-      <c r="B132" s="10">
+      <c r="B132" s="4">
         <v>1.1200000000000001</v>
       </c>
-      <c r="C132" s="10">
+      <c r="C132" s="4">
         <v>102.44</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A133" s="9">
+      <c r="A133" s="3">
         <v>804.64</v>
       </c>
-      <c r="B133" s="10">
+      <c r="B133" s="4">
         <v>1.18</v>
       </c>
-      <c r="C133" s="10">
+      <c r="C133" s="4">
         <v>101.46</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A134" s="9">
+      <c r="A134" s="3">
         <v>635.98</v>
       </c>
-      <c r="B134" s="10">
+      <c r="B134" s="4">
         <v>0.85</v>
       </c>
-      <c r="C134" s="10">
+      <c r="C134" s="4">
         <v>88.53</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A135" s="9">
+      <c r="A135" s="3">
         <v>721.08</v>
       </c>
-      <c r="B135" s="10">
+      <c r="B135" s="4">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C135" s="10">
+      <c r="C135" s="4">
         <v>102.54</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A136" s="9">
+      <c r="A136" s="3">
         <v>736.8</v>
       </c>
-      <c r="B136" s="10">
+      <c r="B136" s="4">
         <v>0.98</v>
       </c>
-      <c r="C136" s="10">
+      <c r="C136" s="4">
         <v>103.17</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A137" s="9">
+      <c r="A137" s="3">
         <v>776.82</v>
       </c>
-      <c r="B137" s="10">
+      <c r="B137" s="4">
         <v>1.19</v>
       </c>
-      <c r="C137" s="10">
+      <c r="C137" s="4">
         <v>103.26</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A138" s="9">
+      <c r="A138" s="3">
         <v>733.59</v>
       </c>
-      <c r="B138" s="10">
+      <c r="B138" s="4">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C138" s="10">
+      <c r="C138" s="4">
         <v>109.44</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A139" s="9">
+      <c r="A139" s="3">
         <v>722.94</v>
       </c>
-      <c r="B139" s="10">
+      <c r="B139" s="4">
         <v>1.17</v>
       </c>
-      <c r="C139" s="10">
+      <c r="C139" s="4">
         <v>105.74</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A140" s="9">
+      <c r="A140" s="3">
         <v>590.37</v>
       </c>
-      <c r="B140" s="10">
+      <c r="B140" s="4">
         <v>0.81</v>
       </c>
-      <c r="C140" s="10">
+      <c r="C140" s="4">
         <v>91.31</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A141" s="9">
+      <c r="A141" s="3">
         <v>620.66</v>
       </c>
-      <c r="B141" s="10">
+      <c r="B141" s="4">
         <v>0.92</v>
       </c>
-      <c r="C141" s="10">
+      <c r="C141" s="4">
         <v>108.5</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A142" s="9">
+      <c r="A142" s="3">
         <v>773.78</v>
       </c>
-      <c r="B142" s="10">
+      <c r="B142" s="4">
         <v>0.96</v>
       </c>
-      <c r="C142" s="10">
+      <c r="C142" s="4">
         <v>100.51</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A143" s="9">
+      <c r="A143" s="3">
         <v>755.07</v>
       </c>
-      <c r="B143" s="10">
+      <c r="B143" s="4">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C143" s="10">
+      <c r="C143" s="4">
         <v>111.26</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A144" s="9">
+      <c r="A144" s="3">
         <v>665.8</v>
       </c>
-      <c r="B144" s="10">
+      <c r="B144" s="4">
         <v>0.99</v>
       </c>
-      <c r="C144" s="10">
+      <c r="C144" s="4">
         <v>104.5</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A145" s="9">
+      <c r="A145" s="3">
         <v>534.79</v>
       </c>
-      <c r="B145" s="10">
+      <c r="B145" s="4">
         <v>0.75</v>
       </c>
-      <c r="C145" s="10">
+      <c r="C145" s="4">
         <v>85.67</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A146" s="9">
+      <c r="A146" s="3">
         <v>653.1</v>
       </c>
-      <c r="B146" s="10">
+      <c r="B146" s="4">
         <v>1.04</v>
       </c>
-      <c r="C146" s="10">
+      <c r="C146" s="4">
         <v>101.58</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A147" s="9">
+      <c r="A147" s="3">
         <v>625.55999999999995</v>
       </c>
-      <c r="B147" s="10">
+      <c r="B147" s="4">
         <v>0.85</v>
       </c>
-      <c r="C147" s="10">
+      <c r="C147" s="4">
         <v>89.9</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A148" s="9">
+      <c r="A148" s="3">
         <v>702.82</v>
       </c>
-      <c r="B148" s="10">
+      <c r="B148" s="4">
         <v>1.07</v>
       </c>
-      <c r="C148" s="10">
+      <c r="C148" s="4">
         <v>97.91</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A149" s="9">
+      <c r="A149" s="3">
         <v>750.19</v>
       </c>
-      <c r="B149" s="10">
+      <c r="B149" s="4">
         <v>1.21</v>
       </c>
-      <c r="C149" s="10">
+      <c r="C149" s="4">
         <v>114.84</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A150" s="9">
+      <c r="A150" s="3">
         <v>676.29</v>
       </c>
-      <c r="B150" s="10">
+      <c r="B150" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C150" s="10">
+      <c r="C150" s="4">
         <v>100.45</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A151" s="9">
+      <c r="A151" s="3">
         <v>650.41</v>
       </c>
-      <c r="B151" s="10">
+      <c r="B151" s="4">
         <v>0.94</v>
       </c>
-      <c r="C151" s="10">
+      <c r="C151" s="4">
         <v>95.41</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A152" s="9">
+      <c r="A152" s="3">
         <v>754.97</v>
       </c>
-      <c r="B152" s="10">
+      <c r="B152" s="4">
         <v>1.17</v>
       </c>
-      <c r="C152" s="10">
+      <c r="C152" s="4">
         <v>100.63</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A153" s="9">
+      <c r="A153" s="3">
         <v>729.56</v>
       </c>
-      <c r="B153" s="10">
+      <c r="B153" s="4">
         <v>1.27</v>
       </c>
-      <c r="C153" s="10">
+      <c r="C153" s="4">
         <v>106.48</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A154" s="9">
+      <c r="A154" s="3">
         <v>662.55</v>
       </c>
-      <c r="B154" s="10">
+      <c r="B154" s="4">
         <v>0.98</v>
       </c>
-      <c r="C154" s="10">
+      <c r="C154" s="4">
         <v>91.89</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A155" s="9">
+      <c r="A155" s="3">
         <v>635.71</v>
       </c>
-      <c r="B155" s="10">
+      <c r="B155" s="4">
         <v>0.9</v>
       </c>
-      <c r="C155" s="10">
+      <c r="C155" s="4">
         <v>98.76</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A156" s="9">
+      <c r="A156" s="3">
         <v>784.49</v>
       </c>
-      <c r="B156" s="10">
+      <c r="B156" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C156" s="10">
+      <c r="C156" s="4">
         <v>101.33</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A157" s="9">
+      <c r="A157" s="3">
         <v>657.27</v>
       </c>
-      <c r="B157" s="10">
+      <c r="B157" s="4">
         <v>1.03</v>
       </c>
-      <c r="C157" s="10">
+      <c r="C157" s="4">
         <v>103.46</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A158" s="9">
+      <c r="A158" s="3">
         <v>599.03</v>
       </c>
-      <c r="B158" s="10">
+      <c r="B158" s="4">
         <v>0.9</v>
       </c>
-      <c r="C158" s="10">
+      <c r="C158" s="4">
         <v>96.03</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A159" s="9">
+      <c r="A159" s="3">
         <v>584.07000000000005</v>
       </c>
-      <c r="B159" s="10">
+      <c r="B159" s="4">
         <v>0.84</v>
       </c>
-      <c r="C159" s="10">
+      <c r="C159" s="4">
         <v>92.35</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A160" s="9">
+      <c r="A160" s="3">
         <v>729.29</v>
       </c>
-      <c r="B160" s="10">
+      <c r="B160" s="4">
         <v>1.17</v>
       </c>
-      <c r="C160" s="10">
+      <c r="C160" s="4">
         <v>102.85</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A161" s="9">
+      <c r="A161" s="3">
         <v>676.09</v>
       </c>
-      <c r="B161" s="10">
+      <c r="B161" s="4">
         <v>1.02</v>
       </c>
-      <c r="C161" s="10">
+      <c r="C161" s="4">
         <v>100.62</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A162" s="9">
+      <c r="A162" s="3">
         <v>743.74</v>
       </c>
-      <c r="B162" s="10">
+      <c r="B162" s="4">
         <v>1.33</v>
       </c>
-      <c r="C162" s="10">
+      <c r="C162" s="4">
         <v>109.99</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A163" s="9">
+      <c r="A163" s="3">
         <v>606.6</v>
       </c>
-      <c r="B163" s="10">
+      <c r="B163" s="4">
         <v>0.81</v>
       </c>
-      <c r="C163" s="10">
+      <c r="C163" s="4">
         <v>91.22</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A164" s="9">
+      <c r="A164" s="3">
         <v>578.22</v>
       </c>
-      <c r="B164" s="10">
+      <c r="B164" s="4">
         <v>0.83</v>
       </c>
-      <c r="C164" s="10">
+      <c r="C164" s="4">
         <v>88.61</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A165" s="9">
+      <c r="A165" s="3">
         <v>635.63</v>
       </c>
-      <c r="B165" s="10">
+      <c r="B165" s="4">
         <v>0.92</v>
       </c>
-      <c r="C165" s="10">
+      <c r="C165" s="4">
         <v>91.31</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A166" s="9">
+      <c r="A166" s="3">
         <v>646.04999999999995</v>
       </c>
-      <c r="B166" s="10">
+      <c r="B166" s="4">
         <v>1.03</v>
       </c>
-      <c r="C166" s="10">
+      <c r="C166" s="4">
         <v>100.66</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A167" s="9">
+      <c r="A167" s="3">
         <v>757.77</v>
       </c>
-      <c r="B167" s="10">
+      <c r="B167" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C167" s="10">
+      <c r="C167" s="4">
         <v>102.89</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A168" s="9">
+      <c r="A168" s="3">
         <v>655.76</v>
       </c>
-      <c r="B168" s="10">
+      <c r="B168" s="4">
         <v>0.94</v>
       </c>
-      <c r="C168" s="10">
+      <c r="C168" s="4">
         <v>94.01</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A169" s="9">
+      <c r="A169" s="3">
         <v>692.33</v>
       </c>
-      <c r="B169" s="10">
+      <c r="B169" s="4">
         <v>0.97</v>
       </c>
-      <c r="C169" s="10">
+      <c r="C169" s="4">
         <v>98.06</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A170" s="9">
+      <c r="A170" s="3">
         <v>806.76</v>
       </c>
-      <c r="B170" s="10">
+      <c r="B170" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C170" s="10">
+      <c r="C170" s="4">
         <v>103.78</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A171" s="9">
+      <c r="A171" s="3">
         <v>679.8</v>
       </c>
-      <c r="B171" s="10">
+      <c r="B171" s="4">
         <v>0.99</v>
       </c>
-      <c r="C171" s="10">
+      <c r="C171" s="4">
         <v>96.65</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A172" s="9">
+      <c r="A172" s="3">
         <v>726.74</v>
       </c>
-      <c r="B172" s="10">
+      <c r="B172" s="4">
         <v>1.07</v>
       </c>
-      <c r="C172" s="10">
+      <c r="C172" s="4">
         <v>109.04</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A173" s="9">
+      <c r="A173" s="3">
         <v>695.47</v>
       </c>
-      <c r="B173" s="10">
+      <c r="B173" s="4">
         <v>1.24</v>
       </c>
-      <c r="C173" s="10">
+      <c r="C173" s="4">
         <v>99.97</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A174" s="9">
+      <c r="A174" s="3">
         <v>701.29</v>
       </c>
-      <c r="B174" s="10">
+      <c r="B174" s="4">
         <v>1.02</v>
       </c>
-      <c r="C174" s="10">
+      <c r="C174" s="4">
         <v>93.88</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A175" s="9">
+      <c r="A175" s="3">
         <v>768.9</v>
       </c>
-      <c r="B175" s="10">
+      <c r="B175" s="4">
         <v>1.08</v>
       </c>
-      <c r="C175" s="10">
+      <c r="C175" s="4">
         <v>101.68</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A176" s="9">
+      <c r="A176" s="3">
         <v>789.37</v>
       </c>
-      <c r="B176" s="10">
+      <c r="B176" s="4">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C176" s="10">
+      <c r="C176" s="4">
         <v>102.97</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A177" s="9">
+      <c r="A177" s="3">
         <v>617.84</v>
       </c>
-      <c r="B177" s="10">
+      <c r="B177" s="4">
         <v>1.03</v>
       </c>
-      <c r="C177" s="10">
+      <c r="C177" s="4">
         <v>98.27</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A178" s="9">
+      <c r="A178" s="3">
         <v>723.78</v>
       </c>
-      <c r="B178" s="10">
+      <c r="B178" s="4">
         <v>1.06</v>
       </c>
-      <c r="C178" s="10">
+      <c r="C178" s="4">
         <v>104.75</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A179" s="9">
+      <c r="A179" s="3">
         <v>794.82</v>
       </c>
-      <c r="B179" s="10">
+      <c r="B179" s="4">
         <v>1.24</v>
       </c>
-      <c r="C179" s="10">
+      <c r="C179" s="4">
         <v>99.69</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A180" s="9">
+      <c r="A180" s="3">
         <v>659.34</v>
       </c>
-      <c r="B180" s="10">
+      <c r="B180" s="4">
         <v>1.1200000000000001</v>
       </c>
-      <c r="C180" s="10">
+      <c r="C180" s="4">
         <v>97.95</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A181" s="9">
+      <c r="A181" s="3">
         <v>743.13</v>
       </c>
-      <c r="B181" s="10">
+      <c r="B181" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C181" s="10">
+      <c r="C181" s="4">
         <v>97.45</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A182" s="9">
+      <c r="A182" s="3">
         <v>790.15</v>
       </c>
-      <c r="B182" s="10">
+      <c r="B182" s="4">
         <v>1.25</v>
       </c>
-      <c r="C182" s="10">
+      <c r="C182" s="4">
         <v>109.93</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A183" s="9">
+      <c r="A183" s="3">
         <v>663.49</v>
       </c>
-      <c r="B183" s="10">
+      <c r="B183" s="4">
         <v>1.06</v>
       </c>
-      <c r="C183" s="10">
+      <c r="C183" s="4">
         <v>103.69</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A184" s="9">
+      <c r="A184" s="3">
         <v>768.61</v>
       </c>
-      <c r="B184" s="10">
+      <c r="B184" s="4">
         <v>1.21</v>
       </c>
-      <c r="C184" s="10">
+      <c r="C184" s="4">
         <v>103.49</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A185" s="9">
+      <c r="A185" s="3">
         <v>701.52</v>
       </c>
-      <c r="B185" s="10">
+      <c r="B185" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C185" s="10">
+      <c r="C185" s="4">
         <v>104.73</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A186" s="9">
+      <c r="A186" s="3">
         <v>713.99</v>
       </c>
-      <c r="B186" s="10">
+      <c r="B186" s="4">
         <v>1</v>
       </c>
-      <c r="C186" s="10">
+      <c r="C186" s="4">
         <v>98.27</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A187" s="9">
+      <c r="A187" s="3">
         <v>781.37</v>
       </c>
-      <c r="B187" s="10">
+      <c r="B187" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C187" s="10">
+      <c r="C187" s="4">
         <v>102.98</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A188" s="9">
+      <c r="A188" s="3">
         <v>607.92999999999995</v>
       </c>
-      <c r="B188" s="10">
+      <c r="B188" s="4">
         <v>0.96</v>
       </c>
-      <c r="C188" s="10">
+      <c r="C188" s="4">
         <v>96.89</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A189" s="9">
+      <c r="A189" s="3">
         <v>701.01</v>
       </c>
-      <c r="B189" s="10">
+      <c r="B189" s="4">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C189" s="10">
+      <c r="C189" s="4">
         <v>112.86</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A190" s="9">
+      <c r="A190" s="3">
         <v>794.21</v>
       </c>
-      <c r="B190" s="10">
+      <c r="B190" s="4">
         <v>1.2</v>
       </c>
-      <c r="C190" s="10">
+      <c r="C190" s="4">
         <v>103.36</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A191" s="9">
+      <c r="A191" s="3">
         <v>678.73</v>
       </c>
-      <c r="B191" s="10">
+      <c r="B191" s="4">
         <v>1.05</v>
       </c>
-      <c r="C191" s="10">
+      <c r="C191" s="4">
         <v>101.37</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A192" s="9">
+      <c r="A192" s="3">
         <v>725.97</v>
       </c>
-      <c r="B192" s="10">
+      <c r="B192" s="4">
         <v>1.17</v>
       </c>
-      <c r="C192" s="10">
+      <c r="C192" s="4">
         <v>100.87</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A193" s="9">
+      <c r="A193" s="3">
         <v>745.93</v>
       </c>
-      <c r="B193" s="10">
+      <c r="B193" s="4">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C193" s="10">
+      <c r="C193" s="4">
         <v>97.27</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A194" s="9">
+      <c r="A194" s="3">
         <v>709.49</v>
       </c>
-      <c r="B194" s="10">
+      <c r="B194" s="4">
         <v>0.99</v>
       </c>
-      <c r="C194" s="10">
+      <c r="C194" s="4">
         <v>101.67</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A195" s="9">
+      <c r="A195" s="3">
         <v>727.93</v>
       </c>
-      <c r="B195" s="10">
+      <c r="B195" s="4">
         <v>1.25</v>
       </c>
-      <c r="C195" s="10">
+      <c r="C195" s="4">
         <v>103.32</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A196" s="9">
+      <c r="A196" s="3">
         <v>771.94</v>
       </c>
-      <c r="B196" s="10">
+      <c r="B196" s="4">
         <v>1.02</v>
       </c>
-      <c r="C196" s="10">
+      <c r="C196" s="4">
         <v>102.24</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A197" s="9">
+      <c r="A197" s="3">
         <v>686.17</v>
       </c>
-      <c r="B197" s="10">
+      <c r="B197" s="4">
         <v>0.93</v>
       </c>
-      <c r="C197" s="10">
+      <c r="C197" s="4">
         <v>99.36</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A198" s="9">
+      <c r="A198" s="3">
         <v>678.87</v>
       </c>
-      <c r="B198" s="10">
+      <c r="B198" s="4">
         <v>0.95</v>
       </c>
-      <c r="C198" s="10">
+      <c r="C198" s="4">
         <v>95.92</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A199" s="9">
+      <c r="A199" s="3">
         <v>699.19</v>
       </c>
-      <c r="B199" s="10">
+      <c r="B199" s="4">
         <v>1.05</v>
       </c>
-      <c r="C199" s="10">
+      <c r="C199" s="4">
         <v>102.73</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A200" s="9">
+      <c r="A200" s="3">
         <v>797.61</v>
       </c>
-      <c r="B200" s="10">
+      <c r="B200" s="4">
         <v>1.22</v>
       </c>
-      <c r="C200" s="10">
+      <c r="C200" s="4">
         <v>105.3</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A201" s="9">
+      <c r="A201" s="3">
         <v>700.88</v>
       </c>
-      <c r="B201" s="10">
+      <c r="B201" s="4">
         <v>1.04</v>
       </c>
-      <c r="C201" s="10">
+      <c r="C201" s="4">
         <v>104.45</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A202" s="9">
+      <c r="A202" s="3">
         <v>695.38</v>
       </c>
-      <c r="B202" s="10">
+      <c r="B202" s="4">
         <v>1.06</v>
       </c>
-      <c r="C202" s="10">
+      <c r="C202" s="4">
         <v>101.69</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A203" s="9">
+      <c r="A203" s="3">
         <v>683.96</v>
       </c>
-      <c r="B203" s="10">
+      <c r="B203" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C203" s="10">
+      <c r="C203" s="4">
         <v>104.3</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A204" s="9">
+      <c r="A204" s="3">
         <v>558.21</v>
       </c>
-      <c r="B204" s="10">
+      <c r="B204" s="4">
         <v>0.82</v>
       </c>
-      <c r="C204" s="10">
+      <c r="C204" s="4">
         <v>89.95</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A205" s="9">
+      <c r="A205" s="3">
         <v>670.24</v>
       </c>
-      <c r="B205" s="10">
+      <c r="B205" s="4">
         <v>1.1599999999999999</v>
       </c>
-      <c r="C205" s="10">
+      <c r="C205" s="4">
         <v>101.06</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A206" s="9">
+      <c r="A206" s="3">
         <v>646.73</v>
       </c>
-      <c r="B206" s="10">
+      <c r="B206" s="4">
         <v>0.96</v>
       </c>
-      <c r="C206" s="10">
+      <c r="C206" s="4">
         <v>95.72</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A207" s="9">
+      <c r="A207" s="3">
         <v>832.72</v>
       </c>
-      <c r="B207" s="10">
+      <c r="B207" s="4">
         <v>1.31</v>
       </c>
-      <c r="C207" s="10">
+      <c r="C207" s="4">
         <v>114.16</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A208" s="9">
+      <c r="A208" s="3">
         <v>646.91999999999996</v>
       </c>
-      <c r="B208" s="10">
+      <c r="B208" s="4">
         <v>0.93</v>
       </c>
-      <c r="C208" s="10">
+      <c r="C208" s="4">
         <v>94.67</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A209" s="9">
+      <c r="A209" s="3">
         <v>689.79</v>
       </c>
-      <c r="B209" s="10">
+      <c r="B209" s="4">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C209" s="10">
+      <c r="C209" s="4">
         <v>101.68</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A210" s="9">
+      <c r="A210" s="3">
         <v>667.71</v>
       </c>
-      <c r="B210" s="10">
+      <c r="B210" s="4">
         <v>0.96</v>
       </c>
-      <c r="C210" s="10">
+      <c r="C210" s="4">
         <v>94.94</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A211" s="9">
+      <c r="A211" s="3">
         <v>737.08</v>
       </c>
-      <c r="B211" s="10">
+      <c r="B211" s="4">
         <v>1.25</v>
       </c>
-      <c r="C211" s="10">
+      <c r="C211" s="4">
         <v>107.2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A212" s="9">
+      <c r="A212" s="3">
         <v>708.65</v>
       </c>
-      <c r="B212" s="10">
+      <c r="B212" s="4">
         <v>1.02</v>
       </c>
-      <c r="C212" s="10">
+      <c r="C212" s="4">
         <v>104.48</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A213" s="9">
+      <c r="A213" s="3">
         <v>692.87</v>
       </c>
-      <c r="B213" s="10">
+      <c r="B213" s="4">
         <v>1.19</v>
       </c>
-      <c r="C213" s="10">
+      <c r="C213" s="4">
         <v>102.44</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A214" s="9">
+      <c r="A214" s="3">
         <v>678.16</v>
       </c>
-      <c r="B214" s="10">
+      <c r="B214" s="4">
         <v>1</v>
       </c>
-      <c r="C214" s="10">
+      <c r="C214" s="4">
         <v>101.92</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A215" s="9">
+      <c r="A215" s="3">
         <v>599.08000000000004</v>
       </c>
-      <c r="B215" s="10">
+      <c r="B215" s="4">
         <v>0.94</v>
       </c>
-      <c r="C215" s="10">
+      <c r="C215" s="4">
         <v>93.29</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A216" s="9">
+      <c r="A216" s="3">
         <v>625.92999999999995</v>
       </c>
-      <c r="B216" s="10">
+      <c r="B216" s="4">
         <v>1.04</v>
       </c>
-      <c r="C216" s="10">
+      <c r="C216" s="4">
         <v>98.61</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A217" s="9">
+      <c r="A217" s="3">
         <v>645.28</v>
       </c>
-      <c r="B217" s="10">
+      <c r="B217" s="4">
         <v>0.96</v>
       </c>
-      <c r="C217" s="10">
+      <c r="C217" s="4">
         <v>100.12</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A218" s="9">
+      <c r="A218" s="3">
         <v>668.1</v>
       </c>
-      <c r="B218" s="10">
+      <c r="B218" s="4">
         <v>0.93</v>
       </c>
-      <c r="C218" s="10">
+      <c r="C218" s="4">
         <v>106.02</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A219" s="9">
+      <c r="A219" s="3">
         <v>792.62</v>
       </c>
-      <c r="B219" s="10">
+      <c r="B219" s="4">
         <v>1.22</v>
       </c>
-      <c r="C219" s="10">
+      <c r="C219" s="4">
         <v>104.45</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A220" s="9">
+      <c r="A220" s="3">
         <v>539.21</v>
       </c>
-      <c r="B220" s="10">
+      <c r="B220" s="4">
         <v>0.84</v>
       </c>
-      <c r="C220" s="10">
+      <c r="C220" s="4">
         <v>86.14</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A221" s="9">
+      <c r="A221" s="3">
         <v>796.77</v>
       </c>
-      <c r="B221" s="10">
+      <c r="B221" s="4">
         <v>1.3</v>
       </c>
-      <c r="C221" s="10">
+      <c r="C221" s="4">
         <v>119.5</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A222" s="9">
+      <c r="A222" s="3">
         <v>708.93</v>
       </c>
-      <c r="B222" s="10">
+      <c r="B222" s="4">
         <v>1.1100000000000001</v>
       </c>
-      <c r="C222" s="10">
+      <c r="C222" s="4">
         <v>103.76</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A223" s="9">
+      <c r="A223" s="3">
         <v>640.84</v>
       </c>
-      <c r="B223" s="10">
+      <c r="B223" s="4">
         <v>1.04</v>
       </c>
-      <c r="C223" s="10">
+      <c r="C223" s="4">
         <v>96.08</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A224" s="9">
+      <c r="A224" s="3">
         <v>657.56</v>
       </c>
-      <c r="B224" s="10">
+      <c r="B224" s="4">
         <v>0.92</v>
       </c>
-      <c r="C224" s="10">
+      <c r="C224" s="4">
         <v>98.61</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A225" s="9">
+      <c r="A225" s="3">
         <v>683.62</v>
       </c>
-      <c r="B225" s="10">
+      <c r="B225" s="4">
         <v>1.02</v>
       </c>
-      <c r="C225" s="10">
+      <c r="C225" s="4">
         <v>100.85</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A226" s="9">
+      <c r="A226" s="3">
         <v>657.11</v>
       </c>
-      <c r="B226" s="10">
+      <c r="B226" s="4">
         <v>0.99</v>
       </c>
-      <c r="C226" s="10">
+      <c r="C226" s="4">
         <v>104.97</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A227" s="9">
+      <c r="A227" s="3">
         <v>599.54999999999995</v>
       </c>
-      <c r="B227" s="10">
+      <c r="B227" s="4">
         <v>0.87</v>
       </c>
-      <c r="C227" s="10">
+      <c r="C227" s="4">
         <v>92.56</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A228" s="9">
+      <c r="A228" s="3">
         <v>857.74</v>
       </c>
-      <c r="B228" s="10">
+      <c r="B228" s="4">
         <v>1.34</v>
       </c>
-      <c r="C228" s="10">
+      <c r="C228" s="4">
         <v>111.29</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A229" s="9">
+      <c r="A229" s="3">
         <v>668.83</v>
       </c>
-      <c r="B229" s="10">
+      <c r="B229" s="4">
         <v>1.03</v>
       </c>
-      <c r="C229" s="10">
+      <c r="C229" s="4">
         <v>100.02</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A230" s="9">
+      <c r="A230" s="3">
         <v>817.68</v>
       </c>
-      <c r="B230" s="10">
+      <c r="B230" s="4">
         <v>1.18</v>
       </c>
-      <c r="C230" s="10">
+      <c r="C230" s="4">
         <v>110.54</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A231" s="9">
+      <c r="A231" s="3">
         <v>644.45000000000005</v>
       </c>
-      <c r="B231" s="10">
+      <c r="B231" s="4">
         <v>1.18</v>
       </c>
-      <c r="C231" s="10">
+      <c r="C231" s="4">
         <v>100.18</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A232" s="9">
+      <c r="A232" s="3">
         <v>723.25</v>
       </c>
-      <c r="B232" s="10">
+      <c r="B232" s="4">
         <v>1.05</v>
       </c>
-      <c r="C232" s="10">
+      <c r="C232" s="4">
         <v>105.26</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A233" s="9">
+      <c r="A233" s="3">
         <v>674.41</v>
       </c>
-      <c r="B233" s="10">
+      <c r="B233" s="4">
         <v>1.07</v>
       </c>
-      <c r="C233" s="10">
+      <c r="C233" s="4">
         <v>108.88</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A234" s="9">
+      <c r="A234" s="3">
         <v>791.56</v>
       </c>
-      <c r="B234" s="10">
+      <c r="B234" s="4">
         <v>1.1200000000000001</v>
       </c>
-      <c r="C234" s="10">
+      <c r="C234" s="4">
         <v>99.23</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A235" s="9">
+      <c r="A235" s="3">
         <v>683.81</v>
       </c>
-      <c r="B235" s="10">
+      <c r="B235" s="4">
         <v>1.39</v>
       </c>
-      <c r="C235" s="10">
+      <c r="C235" s="4">
         <v>103.4</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A236" s="9">
+      <c r="A236" s="3">
         <v>637.49</v>
       </c>
-      <c r="B236" s="10">
+      <c r="B236" s="4">
         <v>0.91</v>
       </c>
-      <c r="C236" s="10">
+      <c r="C236" s="4">
         <v>98.14</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A237" s="9">
+      <c r="A237" s="3">
         <v>696.65</v>
       </c>
-      <c r="B237" s="10">
+      <c r="B237" s="4">
         <v>1.08</v>
       </c>
-      <c r="C237" s="10">
+      <c r="C237" s="4">
         <v>99.76</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A238" s="9">
+      <c r="A238" s="3">
         <v>741.77</v>
       </c>
-      <c r="B238" s="10">
+      <c r="B238" s="4">
         <v>1</v>
       </c>
-      <c r="C238" s="10">
+      <c r="C238" s="4">
         <v>95.49</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A239" s="9">
+      <c r="A239" s="3">
         <v>771.41</v>
       </c>
-      <c r="B239" s="10">
+      <c r="B239" s="4">
         <v>1.1399999999999999</v>
       </c>
-      <c r="C239" s="10">
+      <c r="C239" s="4">
         <v>105.98</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A240" s="9">
+      <c r="A240" s="3">
         <v>880.7</v>
       </c>
-      <c r="B240" s="10">
+      <c r="B240" s="4">
         <v>1.04</v>
       </c>
-      <c r="C240" s="10">
+      <c r="C240" s="4">
         <v>100.06</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A241" s="9">
+      <c r="A241" s="3">
         <v>604.47</v>
       </c>
-      <c r="B241" s="10">
+      <c r="B241" s="4">
         <v>0.9</v>
       </c>
-      <c r="C241" s="10">
+      <c r="C241" s="4">
         <v>90.91</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A242" s="9">
+      <c r="A242" s="3">
         <v>727.42</v>
       </c>
-      <c r="B242" s="10">
+      <c r="B242" s="4">
         <v>1.08</v>
       </c>
-      <c r="C242" s="10">
+      <c r="C242" s="4">
         <v>108.78</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A243" s="9">
+      <c r="A243" s="3">
         <v>737.54</v>
       </c>
-      <c r="B243" s="10">
+      <c r="B243" s="4">
         <v>1.0900000000000001</v>
       </c>
-      <c r="C243" s="10">
+      <c r="C243" s="4">
         <v>107.31</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A244" s="9">
+      <c r="A244" s="3">
         <v>625</v>
       </c>
-      <c r="B244" s="10">
+      <c r="B244" s="4">
         <v>0.92</v>
       </c>
-      <c r="C244" s="10">
+      <c r="C244" s="4">
         <v>94.61</v>
       </c>
     </row>
@@ -3601,180 +3722,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="A1" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
+      <c r="A2" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
     </row>
     <row r="4" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="6">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="6">
+        <v>90</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="6">
+        <v>15</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="H8" s="7"/>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" s="11" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="12">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="12">
-        <v>90</v>
-      </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="12">
-        <v>15</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="18"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="H8" s="13"/>
-      <c r="I8" s="18"/>
-    </row>
-    <row r="9" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A12" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="14" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="A14" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A15" s="11" t="s">
-        <v>56</v>
+      <c r="A15" s="5" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.5">
-      <c r="A18" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="14">
+      <c r="A17" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="8">
         <f>(B5*B10+B6*1000*B11+B7*1000*B12*0.45)/1000</f>
         <v>0</v>
       </c>
-      <c r="C18" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="C18" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C10:F12"/>
+    <mergeCell ref="C18:F19"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="I6:I8"/>
-    <mergeCell ref="C18:F19"/>
+    <mergeCell ref="C10:F12"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/demos/03_fit_copula_and_wire.xlsx
+++ b/examples/demos/03_fit_copula_and_wire.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A93D14-962A-49BB-885A-690A0C87761E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5F45BE-B44A-4951-BCBB-4B118EBE05EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -444,12 +444,12 @@
     <xf numFmtId="0" fontId="15" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -771,16 +771,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
+      <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
+      <c r="B2" s="21"/>
     </row>
     <row r="4" spans="1:2" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="16" t="s">
@@ -1029,19 +1029,19 @@
       <c r="A1" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
@@ -3725,37 +3725,37 @@
       <c r="A1" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="4" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
@@ -3785,23 +3785,23 @@
         <v>15</v>
       </c>
       <c r="H7" s="7"/>
-      <c r="I7" s="19"/>
+      <c r="I7" s="21"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="H8" s="7"/>
-      <c r="I8" s="19"/>
+      <c r="I8" s="21"/>
     </row>
     <row r="9" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" s="5" t="s">
@@ -3811,41 +3811,41 @@
       <c r="C10" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="14" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="5" t="s">
@@ -3856,13 +3856,13 @@
       <c r="A17" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A18" s="5" t="s">
@@ -3875,27 +3875,27 @@
       <c r="C18" s="25" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="C10:F12"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C18:F19"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="C10:F12"/>
-    <mergeCell ref="A2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/demos/03_fit_copula_and_wire.xlsx
+++ b/examples/demos/03_fit_copula_and_wire.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timou\source\repos\modelrisk-mcp\examples\demos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5F45BE-B44A-4951-BCBB-4B118EBE05EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2608745-0280-497B-86E5-091F466EED62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -454,10 +454,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3746,7 +3746,7 @@
       <c r="H2" s="21"/>
     </row>
     <row r="4" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="25" t="s">
         <v>53</v>
       </c>
       <c r="B4" s="21"/>
@@ -3773,7 +3773,7 @@
         <v>90</v>
       </c>
       <c r="H6" s="7"/>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="24" t="s">
         <v>56</v>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       <c r="I8" s="21"/>
     </row>
     <row r="9" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>58</v>
       </c>
       <c r="B9" s="21"/>
@@ -3808,7 +3808,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D10" s="21"/>
@@ -3836,7 +3836,7 @@
       <c r="F12" s="21"/>
     </row>
     <row r="14" spans="1:9" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="25" t="s">
         <v>61</v>
       </c>
       <c r="B14" s="21"/>
@@ -3853,7 +3853,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="16.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="25" t="s">
         <v>63</v>
       </c>
       <c r="B17" s="21"/>
@@ -3872,7 +3872,7 @@
         <f>(B5*B10+B6*1000*B11+B7*1000*B12*0.45)/1000</f>
         <v>0</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="24" t="s">
         <v>65</v>
       </c>
       <c r="D18" s="21"/>
@@ -3887,15 +3887,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="C18:F19"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="C10:F12"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C18:F19"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A4:H4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
